--- a/data/trans_orig/IP07A10-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP07A10-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haber podido disfrutar de su tiempo libre en 2007 (tasa de respuesta: 99,4%)</t>
+          <t>Menores según la frecuencia de haber podido disfrutar de su tiempo libre, percibida por el adulto en 2007 (tasa de respuesta: 99,4%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6337</t>
+          <t>6758</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16087</t>
+          <t>15489</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,81%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11882</t>
+          <t>11944</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21906</t>
+          <t>21942</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>29,02%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>53,23%</t>
+          <t>53,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>20570</t>
+          <t>20545</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>35147</t>
+          <t>35080</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>39,61%</t>
+          <t>39,53%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18953</t>
+          <t>17972</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>29952</t>
+          <t>29566</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>39,83%</t>
+          <t>37,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>62,95%</t>
+          <t>62,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14811</t>
+          <t>14598</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24921</t>
+          <t>24563</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>35,99%</t>
+          <t>35,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>60,55%</t>
+          <t>59,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>36323</t>
+          <t>36132</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>52142</t>
+          <t>51122</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>40,93%</t>
+          <t>40,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>58,76%</t>
+          <t>57,61%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7614</t>
+          <t>7417</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17057</t>
+          <t>17417</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>35,85%</t>
+          <t>36,61%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1508</t>
+          <t>1987</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8281</t>
+          <t>8426</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>10632</t>
+          <t>10534</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>23187</t>
+          <t>22770</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>25,66%</t>
         </is>
       </c>
     </row>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3281</t>
+          <t>2984</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2947</t>
+          <t>3270</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,69%</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3861</t>
+          <t>3414</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3536</t>
+          <t>3398</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,83%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6557</t>
+          <t>6650</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14853</t>
+          <t>15244</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>49,55%</t>
+          <t>50,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4269</t>
+          <t>4527</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12352</t>
+          <t>12240</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>40,01%</t>
+          <t>39,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12675</t>
+          <t>13055</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>24955</t>
+          <t>25077</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>41,01%</t>
+          <t>41,21%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9812</t>
+          <t>9536</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18273</t>
+          <t>18380</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>31,82%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>60,96%</t>
+          <t>61,32%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10860</t>
+          <t>10359</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>19647</t>
+          <t>19285</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>33,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>63,65%</t>
+          <t>62,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>23060</t>
+          <t>23023</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>35920</t>
+          <t>35582</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>37,9%</t>
+          <t>37,84%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>59,04%</t>
+          <t>58,48%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2389</t>
+          <t>2279</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8542</t>
+          <t>8623</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4063</t>
+          <t>3958</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>11825</t>
+          <t>11674</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>38,31%</t>
+          <t>37,82%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>7698</t>
+          <t>7757</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>18081</t>
+          <t>17483</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>28,73%</t>
         </is>
       </c>
     </row>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2172</t>
+          <t>3075</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2842</t>
+          <t>2801</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,7 +1809,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,7 +1829,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3202</t>
+          <t>3108</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,7 +1844,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,11%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6275</t>
+          <t>6404</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15245</t>
+          <t>15370</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>46,09%</t>
+          <t>46,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11910</t>
+          <t>11903</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>23043</t>
+          <t>22786</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>42,31%</t>
+          <t>41,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>20932</t>
+          <t>20646</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>35086</t>
+          <t>34844</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>40,08%</t>
+          <t>39,8%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12381</t>
+          <t>12410</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>21766</t>
+          <t>21350</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>37,43%</t>
+          <t>37,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>65,8%</t>
+          <t>64,54%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17131</t>
+          <t>17052</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>28571</t>
+          <t>29051</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>31,31%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>52,46%</t>
+          <t>53,34%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>32306</t>
+          <t>32029</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>47013</t>
+          <t>47563</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>36,9%</t>
+          <t>36,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>53,71%</t>
+          <t>54,33%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2671</t>
+          <t>2544</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9706</t>
+          <t>9491</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>28,69%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>10044</t>
+          <t>10084</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>20518</t>
+          <t>20771</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>37,68%</t>
+          <t>38,14%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>14569</t>
+          <t>14307</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>27283</t>
+          <t>27535</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>31,45%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>17574</t>
+          <t>17483</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>31089</t>
+          <t>30975</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>35,11%</t>
+          <t>34,98%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>18424</t>
+          <t>18347</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>31816</t>
+          <t>32497</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>33,9%</t>
+          <t>34,62%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>39812</t>
+          <t>39490</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>59482</t>
+          <t>59433</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>32,58%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>33227</t>
+          <t>33796</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>48548</t>
+          <t>48875</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>37,53%</t>
+          <t>38,17%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>54,83%</t>
+          <t>55,2%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>39909</t>
+          <t>39644</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>55679</t>
+          <t>56497</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>42,52%</t>
+          <t>42,24%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>59,32%</t>
+          <t>60,19%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>78211</t>
+          <t>77430</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>98757</t>
+          <t>98908</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>42,88%</t>
+          <t>42,45%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>54,14%</t>
+          <t>54,23%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>14205</t>
+          <t>14729</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>27055</t>
+          <t>27544</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>13717</t>
+          <t>13270</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>25658</t>
+          <t>26381</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>31246</t>
+          <t>30657</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>48326</t>
+          <t>48858</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>26,79%</t>
         </is>
       </c>
     </row>
@@ -3123,7 +3123,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4587</t>
+          <t>5100</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3158,7 +3158,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5096</t>
+          <t>4256</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3173,7 +3173,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>730</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>6416</t>
+          <t>7134</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,91%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>627</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>6258</t>
+          <t>5333</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3217</t>
+          <t>3280</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>725</t>
+          <t>667</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6881</t>
+          <t>6123</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,36%</t>
         </is>
       </c>
     </row>
@@ -3461,12 +3461,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>13884</t>
+          <t>13936</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>25236</t>
+          <t>25310</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3476,12 +3476,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>25,91%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>46,91%</t>
+          <t>47,05%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>21321</t>
+          <t>20687</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>33531</t>
+          <t>33890</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>47,82%</t>
+          <t>48,33%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>39148</t>
+          <t>38459</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>56771</t>
+          <t>55825</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>31,04%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>45,81%</t>
+          <t>45,05%</t>
         </is>
       </c>
     </row>
@@ -3574,12 +3574,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>16966</t>
+          <t>16602</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>29155</t>
+          <t>29025</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>30,86%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>54,2%</t>
+          <t>53,96%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,12 +3609,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>29631</t>
+          <t>29196</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>42060</t>
+          <t>43304</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>42,25%</t>
+          <t>41,63%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>59,98%</t>
+          <t>61,75%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,12 +3644,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>49688</t>
+          <t>50104</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>67426</t>
+          <t>67713</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>40,1%</t>
+          <t>40,43%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>54,41%</t>
+          <t>54,64%</t>
         </is>
       </c>
     </row>
@@ -3687,12 +3687,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>6329</t>
+          <t>6536</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>15843</t>
+          <t>16266</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3702,12 +3702,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3229</t>
+          <t>2736</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>10609</t>
+          <t>10412</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3737,12 +3737,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>11031</t>
+          <t>10834</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>22949</t>
+          <t>23038</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>18,59%</t>
         </is>
       </c>
     </row>
@@ -3805,7 +3805,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>4018</t>
+          <t>4120</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3820,7 +3820,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>2776</t>
+          <t>3141</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3855,7 +3855,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>597</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>5126</t>
+          <t>5583</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3890,7 +3890,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,51%</t>
         </is>
       </c>
     </row>
@@ -4143,12 +4143,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>3957</t>
+          <t>4205</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>12153</t>
+          <t>12540</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4158,12 +4158,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5178</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>13173</t>
+          <t>13357</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>36,73%</t>
+          <t>37,24%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>10969</t>
+          <t>11323</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>22591</t>
+          <t>22772</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>29,33%</t>
         </is>
       </c>
     </row>
@@ -4256,12 +4256,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>17044</t>
+          <t>17220</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>27970</t>
+          <t>27751</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4271,12 +4271,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>40,8%</t>
+          <t>41,22%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>66,95%</t>
+          <t>66,42%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4291,12 +4291,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>11939</t>
+          <t>11588</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>21186</t>
+          <t>20955</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4306,12 +4306,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>32,31%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>59,08%</t>
+          <t>58,43%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>32266</t>
+          <t>32416</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>45466</t>
+          <t>46342</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4341,12 +4341,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>41,56%</t>
+          <t>41,75%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>58,56%</t>
+          <t>59,69%</t>
         </is>
       </c>
     </row>
@@ -4369,12 +4369,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>7319</t>
+          <t>7252</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>16918</t>
+          <t>17112</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>40,49%</t>
+          <t>40,96%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4404,12 +4404,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>7024</t>
+          <t>6861</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>15839</t>
+          <t>15913</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4419,12 +4419,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>44,17%</t>
+          <t>44,37%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4439,12 +4439,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>16626</t>
+          <t>16000</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>29097</t>
+          <t>28872</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4454,12 +4454,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>37,48%</t>
+          <t>37,19%</t>
         </is>
       </c>
     </row>
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>70352</t>
+          <t>69795</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>96664</t>
+          <t>95332</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4840,12 +4840,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>32,8%</t>
+          <t>32,34%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>88437</t>
+          <t>89310</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>115135</t>
+          <t>115713</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>27,37%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>35,46%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>166836</t>
+          <t>166267</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>204724</t>
+          <t>201459</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>32,44%</t>
         </is>
       </c>
     </row>
@@ -4938,12 +4938,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>127974</t>
+          <t>128279</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>155226</t>
+          <t>155784</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4953,12 +4953,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>43,42%</t>
+          <t>43,52%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>52,67%</t>
+          <t>52,85%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4973,12 +4973,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>142030</t>
+          <t>142611</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>171758</t>
+          <t>172177</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4988,12 +4988,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>43,52%</t>
+          <t>43,7%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>52,63%</t>
+          <t>52,76%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5008,12 +5008,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>279779</t>
+          <t>278880</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>320564</t>
+          <t>319318</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5023,12 +5023,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>45,05%</t>
+          <t>44,9%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>51,61%</t>
+          <t>51,41%</t>
         </is>
       </c>
     </row>
@@ -5051,12 +5051,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>53691</t>
+          <t>53982</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>76576</t>
+          <t>76468</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5066,12 +5066,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>51914</t>
+          <t>52724</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>74605</t>
+          <t>74333</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5101,12 +5101,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5121,12 +5121,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>112422</t>
+          <t>110751</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>145121</t>
+          <t>144946</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,34%</t>
         </is>
       </c>
     </row>
@@ -5164,12 +5164,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>1691</t>
+          <t>1327</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>8449</t>
+          <t>7734</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5179,12 +5179,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5199,12 +5199,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>666</t>
+          <t>662</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>6226</t>
+          <t>6962</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5219,7 +5219,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>3296</t>
+          <t>3131</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>11942</t>
+          <t>11380</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5249,12 +5249,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>
@@ -5282,7 +5282,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>5901</t>
+          <t>6219</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5297,7 +5297,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5317,7 +5317,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>4650</t>
+          <t>4051</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5332,7 +5332,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>1322</t>
+          <t>1277</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>7673</t>
+          <t>7630</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5367,7 +5367,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,23%</t>
         </is>
       </c>
     </row>
@@ -5546,7 +5546,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haber podido disfrutar de su tiempo libre en 2012 (tasa de respuesta: 98,02%)</t>
+          <t>Menores según la frecuencia de haber podido disfrutar de su tiempo libre, percibida por el adulto en 2012 (tasa de respuesta: 98,02%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5741,12 +5741,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11686</t>
+          <t>11212</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21362</t>
+          <t>22172</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5756,12 +5756,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>54,02%</t>
+          <t>56,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5776,12 +5776,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7260</t>
+          <t>7159</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16138</t>
+          <t>15851</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5791,12 +5791,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>46,31%</t>
+          <t>45,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5811,12 +5811,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>21180</t>
+          <t>19895</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>35129</t>
+          <t>34210</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5826,12 +5826,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>26,74%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>47,22%</t>
+          <t>45,99%</t>
         </is>
       </c>
     </row>
@@ -5854,12 +5854,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13771</t>
+          <t>13179</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23994</t>
+          <t>23662</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,83%</t>
+          <t>33,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>60,68%</t>
+          <t>59,84%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5889,12 +5889,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10428</t>
+          <t>10469</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19441</t>
+          <t>19868</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5904,12 +5904,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>30,04%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>55,78%</t>
+          <t>57,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5924,12 +5924,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>26836</t>
+          <t>27275</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>40927</t>
+          <t>41036</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5939,12 +5939,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>36,07%</t>
+          <t>36,66%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>55,01%</t>
+          <t>55,16%</t>
         </is>
       </c>
     </row>
@@ -5967,12 +5967,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1130</t>
+          <t>1168</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7001</t>
+          <t>6942</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6002,12 +6002,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3815</t>
+          <t>4407</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11560</t>
+          <t>11742</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
+          <t>33,69%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6037,12 +6037,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>6286</t>
+          <t>6578</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>15328</t>
+          <t>16336</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>21,96%</t>
         </is>
       </c>
     </row>
@@ -6085,7 +6085,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3986</t>
+          <t>4124</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6100,7 +6100,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6120,7 +6120,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3538</t>
+          <t>4165</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6135,7 +6135,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6155,7 +6155,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5250</t>
+          <t>5310</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6170,7 +6170,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,14%</t>
         </is>
       </c>
     </row>
@@ -6198,7 +6198,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4151</t>
+          <t>3806</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6213,7 +6213,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6233,7 +6233,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3365</t>
+          <t>2911</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6268,7 +6268,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4371</t>
+          <t>4448</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,98%</t>
         </is>
       </c>
     </row>
@@ -6423,12 +6423,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10111</t>
+          <t>10081</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19150</t>
+          <t>19320</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6438,12 +6438,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>55,17%</t>
+          <t>55,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6458,12 +6458,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13261</t>
+          <t>13641</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23009</t>
+          <t>23099</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>38,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>65,55%</t>
+          <t>65,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6493,12 +6493,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>26144</t>
+          <t>26358</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>39997</t>
+          <t>39734</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6508,12 +6508,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>37,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>57,29%</t>
+          <t>56,91%</t>
         </is>
       </c>
     </row>
@@ -6536,12 +6536,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12962</t>
+          <t>12575</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>22528</t>
+          <t>22319</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6551,12 +6551,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>37,34%</t>
+          <t>36,22%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>64,9%</t>
+          <t>64,29%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6571,12 +6571,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8236</t>
+          <t>7791</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17018</t>
+          <t>16748</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>48,48%</t>
+          <t>47,71%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>22247</t>
+          <t>22893</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>36158</t>
+          <t>35824</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>51,79%</t>
+          <t>51,31%</t>
         </is>
       </c>
     </row>
@@ -6649,12 +6649,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>641</t>
+          <t>626</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5944</t>
+          <t>5599</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6664,12 +6664,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6684,12 +6684,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1148</t>
+          <t>675</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6672</t>
+          <t>6939</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2086</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>9731</t>
+          <t>9598</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>13,75%</t>
         </is>
       </c>
     </row>
@@ -6767,7 +6767,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3827</t>
+          <t>2962</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6782,7 +6782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6802,7 +6802,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3936</t>
+          <t>4659</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6817,7 +6817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>618</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5531</t>
+          <t>5425</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6847,12 +6847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,77%</t>
         </is>
       </c>
     </row>
@@ -6915,7 +6915,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2516</t>
+          <t>3326</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6950,7 +6950,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3233</t>
+          <t>2682</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6965,7 +6965,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>3,84%</t>
         </is>
       </c>
     </row>
@@ -7105,12 +7105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8196</t>
+          <t>8187</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17345</t>
+          <t>17494</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7120,12 +7120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>39,68%</t>
+          <t>40,02%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6610</t>
+          <t>6730</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15406</t>
+          <t>15290</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7155,12 +7155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>48,12%</t>
+          <t>47,76%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7175,12 +7175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16937</t>
+          <t>17099</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>29918</t>
+          <t>29357</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7190,12 +7190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>39,51%</t>
+          <t>38,77%</t>
         </is>
       </c>
     </row>
@@ -7218,12 +7218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17808</t>
+          <t>17304</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>28016</t>
+          <t>28365</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7233,12 +7233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>40,74%</t>
+          <t>39,59%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>64,1%</t>
+          <t>64,9%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10655</t>
+          <t>10377</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>19653</t>
+          <t>19235</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7268,12 +7268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>32,42%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>61,39%</t>
+          <t>60,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>30663</t>
+          <t>30939</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>44970</t>
+          <t>45290</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7303,12 +7303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>40,5%</t>
+          <t>40,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>59,39%</t>
+          <t>59,81%</t>
         </is>
       </c>
     </row>
@@ -7331,12 +7331,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4663</t>
+          <t>4742</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>13027</t>
+          <t>13258</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7346,12 +7346,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2717</t>
+          <t>3177</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>9886</t>
+          <t>10017</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7381,12 +7381,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>31,29%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>9780</t>
+          <t>9185</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>20522</t>
+          <t>20497</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>27,07%</t>
         </is>
       </c>
     </row>
@@ -7484,7 +7484,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4466</t>
+          <t>3576</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7499,7 +7499,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7519,7 +7519,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4131</t>
+          <t>3379</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7534,7 +7534,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>4,46%</t>
         </is>
       </c>
     </row>
@@ -7787,12 +7787,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>34667</t>
+          <t>34344</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>49494</t>
+          <t>49551</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7802,12 +7802,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>39,91%</t>
+          <t>39,54%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>56,98%</t>
+          <t>57,05%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>31279</t>
+          <t>32205</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>48444</t>
+          <t>48828</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7837,12 +7837,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>32,38%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>48,71%</t>
+          <t>49,09%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>70745</t>
+          <t>70872</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>92947</t>
+          <t>92343</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7872,12 +7872,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>38,04%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>49,89%</t>
+          <t>49,56%</t>
         </is>
       </c>
     </row>
@@ -7900,12 +7900,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>23124</t>
+          <t>23585</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>37364</t>
+          <t>38029</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7915,12 +7915,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>27,15%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>43,02%</t>
+          <t>43,78%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7935,12 +7935,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>37514</t>
+          <t>37013</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>54739</t>
+          <t>53763</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7950,12 +7950,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>37,72%</t>
+          <t>37,21%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>55,04%</t>
+          <t>54,05%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7970,12 +7970,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>65240</t>
+          <t>65123</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>87042</t>
+          <t>86049</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7985,12 +7985,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>35,02%</t>
+          <t>34,95%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>46,72%</t>
+          <t>46,18%</t>
         </is>
       </c>
     </row>
@@ -8013,12 +8013,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>9257</t>
+          <t>9274</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>20773</t>
+          <t>21264</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8028,12 +8028,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8048,12 +8048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>7771</t>
+          <t>7699</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>18702</t>
+          <t>18455</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8063,12 +8063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8083,12 +8083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>19853</t>
+          <t>19964</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>36092</t>
+          <t>35257</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>18,92%</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3422</t>
+          <t>3349</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8146,7 +8146,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8166,7 +8166,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3876</t>
+          <t>4415</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8181,7 +8181,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8196,12 +8196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>610</t>
+          <t>613</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5006</t>
+          <t>4975</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8216,7 +8216,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,67%</t>
         </is>
       </c>
     </row>
@@ -8469,12 +8469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>23290</t>
+          <t>23267</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>37246</t>
+          <t>37218</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>30,58%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>48,96%</t>
+          <t>48,92%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -8504,12 +8504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>25595</t>
+          <t>25629</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>39291</t>
+          <t>39570</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -8519,12 +8519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>35,52%</t>
+          <t>35,56%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>54,52%</t>
+          <t>54,91%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>53017</t>
+          <t>52994</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>72118</t>
+          <t>74290</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>35,79%</t>
+          <t>35,77%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>48,68%</t>
+          <t>50,15%</t>
         </is>
       </c>
     </row>
@@ -8582,12 +8582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>28868</t>
+          <t>28888</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>43213</t>
+          <t>43062</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8597,12 +8597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>37,94%</t>
+          <t>37,97%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>56,8%</t>
+          <t>56,6%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8617,12 +8617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>22230</t>
+          <t>22026</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>36032</t>
+          <t>35844</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8632,12 +8632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>49,74%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -8652,12 +8652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>54798</t>
+          <t>53336</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>73874</t>
+          <t>74653</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8667,12 +8667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>36,99%</t>
+          <t>36,0%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>49,87%</t>
+          <t>50,39%</t>
         </is>
       </c>
     </row>
@@ -8695,12 +8695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>5459</t>
+          <t>5572</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>14626</t>
+          <t>15256</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8710,12 +8710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8730,12 +8730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>6417</t>
+          <t>6243</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>16354</t>
+          <t>15844</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8745,12 +8745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8765,12 +8765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>14468</t>
+          <t>13174</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>27623</t>
+          <t>27195</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8780,12 +8780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,36%</t>
         </is>
       </c>
     </row>
@@ -8813,7 +8813,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3572</t>
+          <t>3199</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8828,7 +8828,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8883,7 +8883,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>2541</t>
+          <t>3160</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8898,7 +8898,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>2,13%</t>
         </is>
       </c>
     </row>
@@ -8961,7 +8961,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3491</t>
+          <t>3629</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8976,7 +8976,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8996,7 +8996,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>3462</t>
+          <t>4186</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9011,7 +9011,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,83%</t>
         </is>
       </c>
     </row>
@@ -9151,12 +9151,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>2608</t>
+          <t>2226</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>9516</t>
+          <t>8956</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -9166,12 +9166,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>36,0%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>7261</t>
+          <t>6996</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>16606</t>
+          <t>16717</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>44,39%</t>
+          <t>44,69%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>11691</t>
+          <t>11412</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>23287</t>
+          <t>22851</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -9236,12 +9236,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>37,38%</t>
+          <t>36,68%</t>
         </is>
       </c>
     </row>
@@ -9264,12 +9264,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>10327</t>
+          <t>10356</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>18769</t>
+          <t>18153</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>41,5%</t>
+          <t>41,62%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>75,43%</t>
+          <t>72,96%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9299,12 +9299,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>13638</t>
+          <t>13513</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>23905</t>
+          <t>23271</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9314,12 +9314,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>36,12%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>63,9%</t>
+          <t>62,2%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -9334,12 +9334,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>26183</t>
+          <t>25982</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>39173</t>
+          <t>38593</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9349,12 +9349,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>42,03%</t>
+          <t>41,71%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>62,88%</t>
+          <t>61,95%</t>
         </is>
       </c>
     </row>
@@ -9377,12 +9377,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2102</t>
+          <t>2242</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>9573</t>
+          <t>9383</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9392,12 +9392,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>38,47%</t>
+          <t>37,71%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9412,12 +9412,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>2681</t>
+          <t>3187</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>10330</t>
+          <t>10195</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9427,12 +9427,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9447,12 +9447,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>6605</t>
+          <t>6809</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>16874</t>
+          <t>16502</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9462,12 +9462,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>26,49%</t>
         </is>
       </c>
     </row>
@@ -9530,7 +9530,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>3682</t>
+          <t>2967</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -9545,7 +9545,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -9565,7 +9565,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>3610</t>
+          <t>4021</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9580,7 +9580,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>6,46%</t>
         </is>
       </c>
     </row>
@@ -9643,7 +9643,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>4045</t>
+          <t>4122</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -9658,7 +9658,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9678,7 +9678,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>3706</t>
+          <t>3672</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9693,7 +9693,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,89%</t>
         </is>
       </c>
     </row>
@@ -9833,12 +9833,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>105006</t>
+          <t>106013</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>134075</t>
+          <t>134375</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -9848,12 +9848,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>34,34%</t>
+          <t>34,67%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>43,85%</t>
+          <t>43,94%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>109706</t>
+          <t>111147</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>138927</t>
+          <t>139137</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -9883,12 +9883,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>35,29%</t>
+          <t>35,75%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>44,69%</t>
+          <t>44,75%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>224638</t>
+          <t>225193</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>266228</t>
+          <t>265811</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -9918,12 +9918,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>36,52%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>43,17%</t>
+          <t>43,1%</t>
         </is>
       </c>
     </row>
@@ -9946,12 +9946,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>123516</t>
+          <t>122872</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>153641</t>
+          <t>152695</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -9961,12 +9961,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>40,39%</t>
+          <t>40,18%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>50,25%</t>
+          <t>49,94%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -9981,12 +9981,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>119600</t>
+          <t>120409</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>149292</t>
+          <t>147721</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -9996,12 +9996,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>38,47%</t>
+          <t>38,73%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>48,02%</t>
+          <t>47,51%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10016,12 +10016,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>252309</t>
+          <t>252393</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>294767</t>
+          <t>294044</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10031,12 +10031,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>40,91%</t>
+          <t>40,93%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>47,8%</t>
+          <t>47,68%</t>
         </is>
       </c>
     </row>
@@ -10059,12 +10059,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>33171</t>
+          <t>33311</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>53506</t>
+          <t>53186</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10094,12 +10094,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>35702</t>
+          <t>35868</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>56610</t>
+          <t>54897</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10109,12 +10109,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10129,12 +10129,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>73790</t>
+          <t>74963</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>103037</t>
+          <t>103159</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10144,12 +10144,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,73%</t>
         </is>
       </c>
     </row>
@@ -10172,12 +10172,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>790</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>6467</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -10187,12 +10187,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -10207,12 +10207,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>1972</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>9539</t>
+          <t>8894</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -10222,12 +10222,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -10242,12 +10242,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>3882</t>
+          <t>3964</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>12833</t>
+          <t>12979</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -10257,12 +10257,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,1%</t>
         </is>
       </c>
     </row>
@@ -10290,7 +10290,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>4918</t>
+          <t>3466</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -10305,7 +10305,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -10320,12 +10320,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>1195</t>
+          <t>1173</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>7371</t>
+          <t>6427</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -10340,7 +10340,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -10355,12 +10355,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>1380</t>
+          <t>1509</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>7673</t>
+          <t>8315</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -10370,12 +10370,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,35%</t>
         </is>
       </c>
     </row>
@@ -10554,7 +10554,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haber podido disfrutar de su tiempo libre en 2016 (tasa de respuesta: 98,92%)</t>
+          <t>Menores según la frecuencia de haber podido disfrutar de su tiempo libre, percibida por el adulto en 2016 (tasa de respuesta: 98,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10749,12 +10749,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10857</t>
+          <t>10960</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20226</t>
+          <t>20542</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10764,12 +10764,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>31,36%</t>
+          <t>31,66%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>58,43%</t>
+          <t>59,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10784,12 +10784,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13521</t>
+          <t>13610</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23934</t>
+          <t>24447</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10799,12 +10799,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>35,31%</t>
+          <t>35,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>62,51%</t>
+          <t>63,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10819,12 +10819,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>27505</t>
+          <t>27576</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>41483</t>
+          <t>41724</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>37,73%</t>
+          <t>37,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>56,9%</t>
+          <t>57,23%</t>
         </is>
       </c>
     </row>
@@ -10862,12 +10862,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7510</t>
+          <t>7710</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16984</t>
+          <t>17816</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10877,12 +10877,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>49,06%</t>
+          <t>51,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10897,12 +10897,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10369</t>
+          <t>10196</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20106</t>
+          <t>20531</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10912,12 +10912,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>52,51%</t>
+          <t>53,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10932,12 +10932,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>20401</t>
+          <t>20008</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>34745</t>
+          <t>34287</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10947,12 +10947,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>47,66%</t>
+          <t>47,03%</t>
         </is>
       </c>
     </row>
@@ -10975,12 +10975,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2658</t>
+          <t>2397</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9444</t>
+          <t>9494</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10990,12 +10990,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11010,12 +11010,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1826</t>
+          <t>1413</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8163</t>
+          <t>7918</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11025,12 +11025,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11045,12 +11045,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5233</t>
+          <t>5308</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>14599</t>
+          <t>14563</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>19,97%</t>
         </is>
       </c>
     </row>
@@ -11093,7 +11093,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5322</t>
+          <t>5348</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11108,7 +11108,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11128,7 +11128,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2621</t>
+          <t>2608</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11143,7 +11143,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11158,12 +11158,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>627</t>
+          <t>630</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6029</t>
+          <t>5724</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11178,7 +11178,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>7,85%</t>
         </is>
       </c>
     </row>
@@ -11431,12 +11431,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12502</t>
+          <t>12288</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23623</t>
+          <t>24134</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11446,12 +11446,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>45,02%</t>
+          <t>45,99%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11466,12 +11466,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14815</t>
+          <t>15117</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26308</t>
+          <t>26786</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11481,12 +11481,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>54,31%</t>
+          <t>55,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11501,12 +11501,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>31337</t>
+          <t>31124</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>47579</t>
+          <t>47309</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>31,05%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>47,15%</t>
+          <t>46,88%</t>
         </is>
       </c>
     </row>
@@ -11544,12 +11544,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>22212</t>
+          <t>22262</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>34697</t>
+          <t>34627</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11559,12 +11559,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>42,33%</t>
+          <t>42,42%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>66,12%</t>
+          <t>65,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11579,12 +11579,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>15405</t>
+          <t>15036</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>27385</t>
+          <t>26740</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11594,12 +11594,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,8%</t>
+          <t>31,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>56,53%</t>
+          <t>55,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11614,12 +11614,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>41534</t>
+          <t>42114</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>58428</t>
+          <t>58194</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11629,12 +11629,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>41,16%</t>
+          <t>41,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>57,9%</t>
+          <t>57,66%</t>
         </is>
       </c>
     </row>
@@ -11657,12 +11657,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2414</t>
+          <t>2660</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10230</t>
+          <t>9774</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11672,12 +11672,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11692,12 +11692,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2328</t>
+          <t>2239</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9930</t>
+          <t>9562</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11707,12 +11707,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11727,12 +11727,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>6432</t>
+          <t>6586</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>17613</t>
+          <t>17215</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11742,12 +11742,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,06%</t>
         </is>
       </c>
     </row>
@@ -11810,7 +11810,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4553</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11825,7 +11825,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11845,7 +11845,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4930</t>
+          <t>5071</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11860,7 +11860,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,03%</t>
         </is>
       </c>
     </row>
@@ -12113,12 +12113,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6455</t>
+          <t>6318</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15160</t>
+          <t>15296</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12128,12 +12128,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>53,95%</t>
+          <t>54,43%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12148,12 +12148,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7741</t>
+          <t>8309</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18198</t>
+          <t>18379</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12163,12 +12163,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>44,38%</t>
+          <t>44,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12183,12 +12183,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>17761</t>
+          <t>17811</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>29958</t>
+          <t>30518</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12198,12 +12198,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>43,35%</t>
+          <t>44,16%</t>
         </is>
       </c>
     </row>
@@ -12226,12 +12226,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7461</t>
+          <t>7333</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16024</t>
+          <t>16000</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12241,12 +12241,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>57,02%</t>
+          <t>56,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12261,12 +12261,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17439</t>
+          <t>16945</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>28196</t>
+          <t>27161</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12276,12 +12276,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>42,53%</t>
+          <t>41,32%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>68,76%</t>
+          <t>66,24%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12296,12 +12296,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>26877</t>
+          <t>27601</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>40958</t>
+          <t>40972</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12311,12 +12311,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>38,89%</t>
+          <t>39,94%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>59,27%</t>
+          <t>59,29%</t>
         </is>
       </c>
     </row>
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1918</t>
+          <t>1840</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8195</t>
+          <t>7994</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12354,12 +12354,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>28,44%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12374,12 +12374,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2062</t>
+          <t>2054</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>9506</t>
+          <t>9570</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12389,12 +12389,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12409,12 +12409,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>5019</t>
+          <t>5387</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>14303</t>
+          <t>14202</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12424,12 +12424,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,55%</t>
         </is>
       </c>
     </row>
@@ -12457,7 +12457,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4796</t>
+          <t>5432</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12472,7 +12472,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12492,7 +12492,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4595</t>
+          <t>3146</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12507,7 +12507,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12527,7 +12527,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5592</t>
+          <t>6089</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12542,7 +12542,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,81%</t>
         </is>
       </c>
     </row>
@@ -12570,7 +12570,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2681</t>
+          <t>3121</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12585,7 +12585,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12640,7 +12640,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3735</t>
+          <t>3305</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12655,7 +12655,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>4,78%</t>
         </is>
       </c>
     </row>
@@ -12795,12 +12795,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>45230</t>
+          <t>45729</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>63152</t>
+          <t>63777</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>39,29%</t>
+          <t>39,72%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>54,86%</t>
+          <t>55,4%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>32667</t>
+          <t>33308</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>49865</t>
+          <t>50756</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>32,17%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>48,16%</t>
+          <t>49,02%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12865,12 +12865,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>85066</t>
+          <t>85167</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>109440</t>
+          <t>109510</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12880,12 +12880,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>38,95%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>50,05%</t>
+          <t>50,08%</t>
         </is>
       </c>
     </row>
@@ -12908,12 +12908,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>33945</t>
+          <t>32565</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>49449</t>
+          <t>50146</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>42,95%</t>
+          <t>43,56%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>37932</t>
+          <t>37112</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>54563</t>
+          <t>54648</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>35,84%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>52,7%</t>
+          <t>52,78%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12978,12 +12978,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>74408</t>
+          <t>74361</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>99394</t>
+          <t>99548</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12993,12 +12993,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>34,01%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>45,46%</t>
+          <t>45,53%</t>
         </is>
       </c>
     </row>
@@ -13021,12 +13021,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>11339</t>
+          <t>10982</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>24188</t>
+          <t>23598</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13036,12 +13036,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13056,12 +13056,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>8328</t>
+          <t>7622</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>20774</t>
+          <t>19402</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13071,12 +13071,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13091,12 +13091,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>22091</t>
+          <t>22254</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>39505</t>
+          <t>38745</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13106,12 +13106,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>17,72%</t>
         </is>
       </c>
     </row>
@@ -13139,7 +13139,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3882</t>
+          <t>3875</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13169,12 +13169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>759</t>
+          <t>758</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7110</t>
+          <t>6768</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13189,7 +13189,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13204,12 +13204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1042</t>
+          <t>1003</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>8012</t>
+          <t>8199</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13219,12 +13219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,75%</t>
         </is>
       </c>
     </row>
@@ -13252,7 +13252,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5136</t>
+          <t>5185</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13267,7 +13267,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13287,7 +13287,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4455</t>
+          <t>3768</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13302,7 +13302,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13317,12 +13317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>689</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5131</t>
+          <t>5834</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13332,12 +13332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,67%</t>
         </is>
       </c>
     </row>
@@ -13477,12 +13477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>23205</t>
+          <t>22479</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>37980</t>
+          <t>37301</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13492,12 +13492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>49,95%</t>
+          <t>49,05%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13512,12 +13512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>22729</t>
+          <t>23151</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>38335</t>
+          <t>37313</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13527,12 +13527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>31,48%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>52,13%</t>
+          <t>50,74%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13547,12 +13547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>50173</t>
+          <t>50932</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>71047</t>
+          <t>71035</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13562,12 +13562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>34,05%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>47,5%</t>
+          <t>47,49%</t>
         </is>
       </c>
     </row>
@@ -13590,12 +13590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>28190</t>
+          <t>27740</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>42197</t>
+          <t>41970</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13605,12 +13605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>37,07%</t>
+          <t>36,48%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>55,49%</t>
+          <t>55,19%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13625,12 +13625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>26333</t>
+          <t>27054</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>41254</t>
+          <t>41366</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13640,12 +13640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>36,79%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>56,1%</t>
+          <t>56,25%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13660,12 +13660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>58257</t>
+          <t>58975</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>79083</t>
+          <t>79500</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13675,12 +13675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>38,95%</t>
+          <t>39,43%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>52,87%</t>
+          <t>53,15%</t>
         </is>
       </c>
     </row>
@@ -13703,12 +13703,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>4357</t>
+          <t>4333</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>14072</t>
+          <t>13867</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13718,12 +13718,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -13738,12 +13738,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>4778</t>
+          <t>4913</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>14404</t>
+          <t>14100</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13753,12 +13753,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -13773,12 +13773,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>10889</t>
+          <t>10988</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>24235</t>
+          <t>24991</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -13788,12 +13788,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,71%</t>
         </is>
       </c>
     </row>
@@ -13821,7 +13821,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>4475</t>
+          <t>3942</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -13836,7 +13836,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -13856,7 +13856,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>5131</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -13871,7 +13871,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -13886,12 +13886,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>640</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>6351</t>
+          <t>6646</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -13906,7 +13906,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,44%</t>
         </is>
       </c>
     </row>
@@ -13934,7 +13934,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>4064</t>
+          <t>4076</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -13949,7 +13949,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -14004,7 +14004,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>4060</t>
+          <t>3841</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14019,7 +14019,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,57%</t>
         </is>
       </c>
     </row>
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>4983</t>
+          <t>5472</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>13382</t>
+          <t>14078</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -14174,12 +14174,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>41,57%</t>
+          <t>43,73%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -14194,12 +14194,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>8611</t>
+          <t>9026</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>18827</t>
+          <t>18346</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -14209,12 +14209,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>48,7%</t>
+          <t>47,46%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -14229,12 +14229,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>16592</t>
+          <t>16369</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>29633</t>
+          <t>29009</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -14244,12 +14244,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>41,82%</t>
+          <t>40,94%</t>
         </is>
       </c>
     </row>
@@ -14272,12 +14272,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>11838</t>
+          <t>11917</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>21416</t>
+          <t>21062</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -14287,12 +14287,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>36,77%</t>
+          <t>37,02%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>66,52%</t>
+          <t>65,42%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -14307,12 +14307,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>12481</t>
+          <t>12789</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>22979</t>
+          <t>23354</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -14322,12 +14322,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>32,29%</t>
+          <t>33,08%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>59,44%</t>
+          <t>60,41%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -14342,12 +14342,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>26298</t>
+          <t>27036</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>40877</t>
+          <t>40793</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -14357,12 +14357,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>37,12%</t>
+          <t>38,16%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>57,69%</t>
+          <t>57,57%</t>
         </is>
       </c>
     </row>
@@ -14385,12 +14385,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1232</t>
+          <t>1243</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>7589</t>
+          <t>7618</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -14400,12 +14400,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -14420,12 +14420,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>3028</t>
+          <t>2981</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>11551</t>
+          <t>11285</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -14435,12 +14435,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>29,19%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -14455,12 +14455,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>6365</t>
+          <t>5988</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>16398</t>
+          <t>16122</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -14470,12 +14470,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>22,75%</t>
         </is>
       </c>
     </row>
@@ -14498,12 +14498,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>581</t>
+          <t>558</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>5638</t>
+          <t>5780</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -14513,12 +14513,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -14538,7 +14538,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>3697</t>
+          <t>3497</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -14553,7 +14553,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -14568,12 +14568,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>795</t>
+          <t>803</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>7418</t>
+          <t>7355</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -14583,12 +14583,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,38%</t>
         </is>
       </c>
     </row>
@@ -14616,7 +14616,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>3737</t>
+          <t>4535</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -14631,7 +14631,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -14686,7 +14686,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>3832</t>
+          <t>3856</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -14701,7 +14701,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,44%</t>
         </is>
       </c>
     </row>
@@ -14841,12 +14841,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>122338</t>
+          <t>124403</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>152768</t>
+          <t>154151</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -14856,12 +14856,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>36,14%</t>
+          <t>36,75%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>45,12%</t>
+          <t>45,53%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -14876,12 +14876,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>123596</t>
+          <t>123276</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>154761</t>
+          <t>153158</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -14891,12 +14891,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>35,98%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>45,06%</t>
+          <t>44,59%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -14911,12 +14911,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>257598</t>
+          <t>250912</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>298760</t>
+          <t>296044</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -14926,12 +14926,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>37,77%</t>
+          <t>36,79%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>43,8%</t>
+          <t>43,41%</t>
         </is>
       </c>
     </row>
@@ -14954,12 +14954,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>130143</t>
+          <t>129762</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>161174</t>
+          <t>160695</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -14969,12 +14969,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>38,33%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>47,61%</t>
+          <t>47,46%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -14989,12 +14989,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>139898</t>
+          <t>140728</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>171449</t>
+          <t>170735</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -15004,12 +15004,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>40,73%</t>
+          <t>40,97%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>49,92%</t>
+          <t>49,71%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -15024,12 +15024,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>278758</t>
+          <t>281322</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>322617</t>
+          <t>325884</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -15039,12 +15039,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>40,87%</t>
+          <t>41,25%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>47,3%</t>
+          <t>47,78%</t>
         </is>
       </c>
     </row>
@@ -15067,12 +15067,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>34193</t>
+          <t>34461</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>55271</t>
+          <t>55364</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -15082,12 +15082,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -15102,12 +15102,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>32949</t>
+          <t>32720</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>53833</t>
+          <t>53192</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -15117,12 +15117,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -15137,12 +15137,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>70219</t>
+          <t>72709</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>100749</t>
+          <t>101511</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -15152,12 +15152,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,88%</t>
         </is>
       </c>
     </row>
@@ -15180,12 +15180,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>2995</t>
+          <t>3171</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>12335</t>
+          <t>12574</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -15195,12 +15195,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -15215,12 +15215,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>3494</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>13594</t>
+          <t>13469</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -15230,12 +15230,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -15250,12 +15250,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>8529</t>
+          <t>8295</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>21140</t>
+          <t>21122</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -15265,7 +15265,7 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -15293,12 +15293,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>1802</t>
+          <t>1444</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>8158</t>
+          <t>8184</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -15308,12 +15308,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -15333,7 +15333,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>3482</t>
+          <t>3472</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -15363,12 +15363,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>1802</t>
+          <t>1969</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>8658</t>
+          <t>9447</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -15378,12 +15378,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,39%</t>
         </is>
       </c>
     </row>
@@ -15562,7 +15562,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haber podido disfrutar de su tiempo libre en 2023 (tasa de respuesta: 99,79%)</t>
+          <t>Menores según la frecuencia de haber podido disfrutar de su tiempo libre, percibida por el adulto en 2023 (tasa de respuesta: 99,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -15757,12 +15757,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>27679</t>
+          <t>27924</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>41523</t>
+          <t>41857</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -15772,47 +15772,47 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
+          <t>47,55%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>71,27%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>53062</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>39081</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>62172</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>64,0%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
           <t>47,13%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>70,71%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>53062</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>38175</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>61574</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>64,0%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>46,04%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>74,26%</t>
+          <t>74,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -15827,12 +15827,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>72356</t>
+          <t>75495</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>100876</t>
+          <t>100909</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -15842,12 +15842,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>51,08%</t>
+          <t>53,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>71,22%</t>
+          <t>71,24%</t>
         </is>
       </c>
     </row>
@@ -15870,12 +15870,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12381</t>
+          <t>12843</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26438</t>
+          <t>26418</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -15885,12 +15885,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>45,02%</t>
+          <t>44,98%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -15905,12 +15905,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12507</t>
+          <t>12494</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>29938</t>
+          <t>30872</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -15920,12 +15920,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,11%</t>
+          <t>37,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -15940,12 +15940,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>28301</t>
+          <t>28225</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>52051</t>
+          <t>49751</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -15955,12 +15955,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>35,12%</t>
         </is>
       </c>
     </row>
@@ -15983,12 +15983,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1572</t>
+          <t>1486</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9048</t>
+          <t>8036</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -15998,12 +15998,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -16018,12 +16018,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2375</t>
+          <t>2554</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>23740</t>
+          <t>29640</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -16033,12 +16033,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>35,75%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -16053,12 +16053,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5288</t>
+          <t>5808</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>32281</t>
+          <t>34266</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -16068,12 +16068,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>24,19%</t>
         </is>
       </c>
     </row>
@@ -16214,7 +16214,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4218</t>
+          <t>4024</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -16229,7 +16229,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -16249,7 +16249,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3709</t>
+          <t>3576</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -16264,7 +16264,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -16279,12 +16279,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>528</t>
+          <t>531</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>5635</t>
+          <t>5755</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -16299,7 +16299,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,06%</t>
         </is>
       </c>
     </row>
@@ -16439,12 +16439,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>31431</t>
+          <t>31731</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>42447</t>
+          <t>43120</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -16454,12 +16454,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>57,66%</t>
+          <t>58,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>77,87%</t>
+          <t>79,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -16474,12 +16474,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>23985</t>
+          <t>23256</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>37479</t>
+          <t>37105</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -16489,12 +16489,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>43,98%</t>
+          <t>42,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>68,73%</t>
+          <t>68,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -16509,12 +16509,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>58098</t>
+          <t>59149</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>76430</t>
+          <t>77149</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -16524,12 +16524,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>53,28%</t>
+          <t>54,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>70,09%</t>
+          <t>70,75%</t>
         </is>
       </c>
     </row>
@@ -16552,12 +16552,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9429</t>
+          <t>9288</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20574</t>
+          <t>19988</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -16567,12 +16567,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,74%</t>
+          <t>36,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -16587,12 +16587,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13905</t>
+          <t>13919</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>27383</t>
+          <t>26829</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -16602,12 +16602,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>50,22%</t>
+          <t>49,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -16622,12 +16622,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>25792</t>
+          <t>25615</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>43617</t>
+          <t>42228</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -16637,12 +16637,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>40,0%</t>
+          <t>38,73%</t>
         </is>
       </c>
     </row>
@@ -16665,12 +16665,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>533</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6101</t>
+          <t>5779</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -16680,12 +16680,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -16705,7 +16705,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6267</t>
+          <t>5624</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -16720,7 +16720,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -16735,12 +16735,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1197</t>
+          <t>1130</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>8628</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -16750,12 +16750,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,42%</t>
         </is>
       </c>
     </row>
@@ -16783,7 +16783,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3446</t>
+          <t>3261</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -16798,7 +16798,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -16818,7 +16818,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7998</t>
+          <t>8488</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -16833,7 +16833,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -16848,12 +16848,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>675</t>
+          <t>666</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10353</t>
+          <t>9943</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -16863,12 +16863,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,12%</t>
         </is>
       </c>
     </row>
@@ -17121,12 +17121,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15121</t>
+          <t>15346</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24302</t>
+          <t>24383</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -17136,12 +17136,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>49,22%</t>
+          <t>49,95%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>79,1%</t>
+          <t>79,37%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -17156,12 +17156,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18232</t>
+          <t>18305</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>28609</t>
+          <t>28305</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -17171,12 +17171,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>52,53%</t>
+          <t>52,74%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>82,43%</t>
+          <t>81,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -17191,12 +17191,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>37036</t>
+          <t>37066</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>50682</t>
+          <t>50636</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -17206,12 +17206,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>56,6%</t>
+          <t>56,65%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>77,46%</t>
+          <t>77,39%</t>
         </is>
       </c>
     </row>
@@ -17234,12 +17234,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2715</t>
+          <t>2593</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10066</t>
+          <t>9865</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -17249,12 +17249,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>32,11%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -17269,12 +17269,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5158</t>
+          <t>5322</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>15837</t>
+          <t>15511</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -17284,12 +17284,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>45,63%</t>
+          <t>44,69%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -17304,12 +17304,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>9819</t>
+          <t>10098</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>22757</t>
+          <t>22376</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -17319,12 +17319,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>34,78%</t>
+          <t>34,2%</t>
         </is>
       </c>
     </row>
@@ -17347,12 +17347,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>1598</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8927</t>
+          <t>8149</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -17362,12 +17362,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -17387,7 +17387,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4216</t>
+          <t>5668</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -17402,7 +17402,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -17417,12 +17417,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2186</t>
+          <t>2362</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>10581</t>
+          <t>10348</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -17432,12 +17432,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>15,82%</t>
         </is>
       </c>
     </row>
@@ -17578,7 +17578,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2763</t>
+          <t>2841</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -17593,7 +17593,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -17648,7 +17648,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3142</t>
+          <t>2861</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -17663,7 +17663,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,37%</t>
         </is>
       </c>
     </row>
@@ -17803,12 +17803,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>28188</t>
+          <t>28323</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>77774</t>
+          <t>78218</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -17818,12 +17818,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>65,68%</t>
+          <t>66,05%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -17838,12 +17838,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>60854</t>
+          <t>60717</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>86776</t>
+          <t>86649</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -17853,12 +17853,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>50,17%</t>
+          <t>50,06%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>71,54%</t>
+          <t>71,43%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -17873,12 +17873,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>90123</t>
+          <t>88831</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>155247</t>
+          <t>156011</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>37,6%</t>
+          <t>37,06%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>64,76%</t>
+          <t>65,08%</t>
         </is>
       </c>
     </row>
@@ -17916,12 +17916,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>33286</t>
+          <t>32530</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>87129</t>
+          <t>87169</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -17931,12 +17931,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>73,58%</t>
+          <t>73,61%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -17951,12 +17951,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>28549</t>
+          <t>28284</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>55134</t>
+          <t>53573</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -17966,12 +17966,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>45,45%</t>
+          <t>44,17%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -17986,12 +17986,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>70369</t>
+          <t>70849</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>140463</t>
+          <t>141220</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -18001,12 +18001,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>58,6%</t>
+          <t>58,91%</t>
         </is>
       </c>
     </row>
@@ -18029,12 +18029,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1488</t>
+          <t>1231</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>9056</t>
+          <t>9150</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -18044,12 +18044,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -18064,12 +18064,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1629</t>
+          <t>1313</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>9047</t>
+          <t>8163</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -18079,12 +18079,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>4207</t>
+          <t>4014</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>14556</t>
+          <t>13865</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -18114,12 +18114,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,78%</t>
         </is>
       </c>
     </row>
@@ -18147,7 +18147,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5349</t>
+          <t>4389</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -18162,7 +18162,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -18182,7 +18182,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3318</t>
+          <t>3824</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -18197,7 +18197,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -18212,12 +18212,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>474</t>
+          <t>545</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5772</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -18227,12 +18227,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -18260,7 +18260,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2516</t>
+          <t>2799</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -18275,7 +18275,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -18295,7 +18295,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>6349</t>
+          <t>7787</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -18310,7 +18310,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -18325,12 +18325,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>616</t>
+          <t>606</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>7802</t>
+          <t>7012</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -18340,12 +18340,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>2,93%</t>
         </is>
       </c>
     </row>
@@ -18485,12 +18485,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>31675</t>
+          <t>31012</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>46317</t>
+          <t>46161</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -18500,12 +18500,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>50,54%</t>
+          <t>49,48%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>73,9%</t>
+          <t>73,65%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -18520,12 +18520,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>54044</t>
+          <t>54069</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>74528</t>
+          <t>74954</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -18535,12 +18535,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>58,64%</t>
+          <t>58,66%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>80,86%</t>
+          <t>81,32%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -18555,12 +18555,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>90036</t>
+          <t>88939</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>115242</t>
+          <t>115789</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -18570,12 +18570,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>58,15%</t>
+          <t>57,44%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>74,42%</t>
+          <t>74,78%</t>
         </is>
       </c>
     </row>
@@ -18598,12 +18598,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>13775</t>
+          <t>14143</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>28893</t>
+          <t>29607</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -18613,12 +18613,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>46,1%</t>
+          <t>47,24%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -18633,12 +18633,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>15515</t>
+          <t>14735</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>33741</t>
+          <t>33787</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -18648,12 +18648,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>36,61%</t>
+          <t>36,66%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -18668,12 +18668,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>33822</t>
+          <t>33841</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>58980</t>
+          <t>59518</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -18683,12 +18683,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>38,44%</t>
         </is>
       </c>
     </row>
@@ -18711,12 +18711,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>167</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>4422</t>
+          <t>4237</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -18731,7 +18731,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -18746,12 +18746,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>619</t>
+          <t>848</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>7559</t>
+          <t>7501</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -18761,12 +18761,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -18781,12 +18781,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1822</t>
+          <t>1686</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>9588</t>
+          <t>8658</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -18796,12 +18796,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>5,59%</t>
         </is>
       </c>
     </row>
@@ -18829,7 +18829,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>4588</t>
+          <t>4425</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -18844,7 +18844,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -18899,7 +18899,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>4446</t>
+          <t>5147</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -18914,7 +18914,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,32%</t>
         </is>
       </c>
     </row>
@@ -18977,7 +18977,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>5071</t>
+          <t>5063</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -18992,7 +18992,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -19012,7 +19012,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>4750</t>
+          <t>5554</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -19027,7 +19027,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,59%</t>
         </is>
       </c>
     </row>
@@ -19167,12 +19167,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>18120</t>
+          <t>18228</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>29464</t>
+          <t>29042</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -19182,12 +19182,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>45,36%</t>
+          <t>45,63%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>73,76%</t>
+          <t>72,7%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -19202,12 +19202,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>19942</t>
+          <t>20139</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>32658</t>
+          <t>32621</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -19217,12 +19217,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>42,47%</t>
+          <t>42,89%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>69,56%</t>
+          <t>69,48%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -19237,12 +19237,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>41472</t>
+          <t>40376</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>58065</t>
+          <t>58341</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -19252,12 +19252,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>47,72%</t>
+          <t>46,46%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>66,82%</t>
+          <t>67,14%</t>
         </is>
       </c>
     </row>
@@ -19280,12 +19280,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>7792</t>
+          <t>8068</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>18730</t>
+          <t>18315</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -19295,12 +19295,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>46,89%</t>
+          <t>45,85%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -19315,12 +19315,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>11634</t>
+          <t>11272</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>23562</t>
+          <t>23413</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -19330,12 +19330,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>24,01%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>50,18%</t>
+          <t>49,87%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -19350,12 +19350,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>22090</t>
+          <t>22595</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>38170</t>
+          <t>38411</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -19365,12 +19365,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>43,92%</t>
+          <t>44,2%</t>
         </is>
       </c>
     </row>
@@ -19393,12 +19393,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>818</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>7550</t>
+          <t>7994</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -19408,12 +19408,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -19428,12 +19428,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>844</t>
+          <t>836</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>8231</t>
+          <t>8381</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -19443,12 +19443,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -19463,12 +19463,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>2259</t>
+          <t>2572</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>12163</t>
+          <t>12946</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,9%</t>
         </is>
       </c>
     </row>
@@ -19624,7 +19624,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>2813</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -19639,7 +19639,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -19694,7 +19694,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1933</t>
+          <t>2387</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -19709,7 +19709,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>
@@ -19849,12 +19849,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>167593</t>
+          <t>160072</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>238352</t>
+          <t>237365</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -19864,12 +19864,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>45,92%</t>
+          <t>43,85%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>65,3%</t>
+          <t>65,03%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -19884,12 +19884,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>247117</t>
+          <t>248212</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>294156</t>
+          <t>293614</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -19899,12 +19899,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>57,13%</t>
+          <t>57,38%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>68,0%</t>
+          <t>67,88%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -19919,12 +19919,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>436494</t>
+          <t>427864</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>519981</t>
+          <t>517875</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -19934,12 +19934,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>54,73%</t>
+          <t>53,65%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>65,2%</t>
+          <t>64,93%</t>
         </is>
       </c>
     </row>
@@ -19962,12 +19962,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>100427</t>
+          <t>100925</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>179388</t>
+          <t>184965</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -19977,12 +19977,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>27,65%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>49,15%</t>
+          <t>50,67%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -19997,12 +19997,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>109909</t>
+          <t>112773</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>152823</t>
+          <t>155336</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -20012,12 +20012,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>35,33%</t>
+          <t>35,91%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -20032,12 +20032,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>225170</t>
+          <t>227781</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>316712</t>
+          <t>327833</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -20047,12 +20047,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>28,56%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>39,71%</t>
+          <t>41,1%</t>
         </is>
       </c>
     </row>
@@ -20075,12 +20075,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>12502</t>
+          <t>12542</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>29546</t>
+          <t>28897</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -20090,12 +20090,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -20110,12 +20110,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>12442</t>
+          <t>12259</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>47380</t>
+          <t>39464</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -20125,12 +20125,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -20145,12 +20145,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>29427</t>
+          <t>28177</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>61904</t>
+          <t>60592</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -20160,12 +20160,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,6%</t>
         </is>
       </c>
     </row>
@@ -20188,12 +20188,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>1005</t>
+          <t>1138</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>7390</t>
+          <t>7581</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -20203,12 +20203,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -20228,7 +20228,7 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>9622</t>
+          <t>8421</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -20243,7 +20243,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -20258,12 +20258,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>2655</t>
+          <t>2952</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>12869</t>
+          <t>14196</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -20273,12 +20273,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,78%</t>
         </is>
       </c>
     </row>
@@ -20301,12 +20301,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>586</t>
+          <t>574</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>5994</t>
+          <t>6033</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -20321,7 +20321,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -20336,12 +20336,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>1253</t>
+          <t>1396</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>8633</t>
+          <t>8481</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -20351,12 +20351,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -20371,12 +20371,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>2791</t>
+          <t>2956</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>11373</t>
+          <t>11933</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -20386,12 +20386,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,5%</t>
         </is>
       </c>
     </row>
